--- a/intake_forms/033_child_relocation_move_away_request_intake_form--intake_forms.xlsx
+++ b/intake_forms/033_child_relocation_move_away_request_intake_form--intake_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -939,8 +939,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -968,12 +968,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'parent',_'value':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Parent', 'value': 'parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'legal_representative',_'value':_'lawyer'}</t>
+          <t>legal_representative</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Legal Representative', 'value': 'lawyer'}</t>
+          <t>Legal Representative</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'mediator',_'value':_'mediator'}</t>
+          <t>mediator</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Mediator', 'value': 'mediator'}</t>
+          <t>Mediator</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'new_employment_opportunity',_'value':_'employment'}</t>
+          <t>new_employment_opportunity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'New Employment Opportunity', 'value': 'employment'}</t>
+          <t>New Employment Opportunity</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'move_closer_to_family_support',_'value':_'family'}</t>
+          <t>move_closer_to_family_support</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Move closer to Family Support', 'value': 'family'}</t>
+          <t>Move closer to Family Support</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'higher_education',_'value':_'education'}</t>
+          <t>higher_education</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Higher Education', 'value': 'education'}</t>
+          <t>Higher Education</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'other_reason',_'value':_'other'}</t>
+          <t>other_reason</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Other Reason', 'value': 'other'}</t>
+          <t>Other Reason</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_notified_and_agrees',_'value':_'yes_agree'}</t>
+          <t>yes_-_notified_and_agrees</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Notified and Agrees', 'value': 'yes_agree'}</t>
+          <t>Yes - Notified and Agrees</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_notified_and_disagrees',_'value':_'yes_disagree'}</t>
+          <t>yes_-_notified_and_disagrees</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Notified and Disagrees', 'value': 'yes_disagree'}</t>
+          <t>Yes - Notified and Disagrees</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_not_yet_notified',_'value':_false}</t>
+          <t>no_-_not_yet_notified</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'No - Not yet notified', 'value': False}</t>
+          <t>No - Not yet notified</t>
         </is>
       </c>
     </row>
